--- a/output/graficos_dimensiones/comunal_p_basica_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:41</t>
+    <t xml:space="preserve">2026-09-09 23:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:40</t>
+    <t xml:space="preserve">2026-09-18 10:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:29</t>
+    <t xml:space="preserve">2026-09-23 13:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:01</t>
+    <t xml:space="preserve">2026-10-02 14:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2018_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2018_los rios.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:44</t>
+    <t xml:space="preserve">2026-10-05 13:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
